--- a/data/Date_landmarks_20essais.xlsx
+++ b/data/Date_landmarks_20essais.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN.RDS-PRET-0218\Desktop\Agrocampus Ouest\M2\Projet ingénieur\meteo_vs_rendement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN.RDS-PRET-0218\Desktop\Agrocampus Ouest\M2\Projet ingénieur\meteo_vs_rendement\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1319B8A0-B84E-43D4-ACCC-D1D9461B28C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1DBEE1D-65E4-4CD6-896C-A32D99521B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -218,10 +218,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -505,8 +504,7 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="7" width="17.81640625" customWidth="1"/>
-    <col min="8" max="8" width="17.81640625" style="2" customWidth="1"/>
+    <col min="2" max="8" width="17.81640625" customWidth="1"/>
     <col min="9" max="10" width="28.1796875" customWidth="1"/>
     <col min="11" max="11" width="16.7265625" customWidth="1"/>
   </cols>
@@ -548,7 +546,7 @@
         <v>20</v>
       </c>
       <c r="D2" s="1">
-        <v>43545</v>
+        <v>40623</v>
       </c>
       <c r="E2">
         <v>21</v>
@@ -559,7 +557,7 @@
       <c r="G2" s="1">
         <v>40549</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2">
         <f t="shared" ref="H2:H21" si="0">_xlfn.DAYS(G2,F2)</f>
         <v>43</v>
       </c>
@@ -588,7 +586,7 @@
       <c r="G3" s="1">
         <v>40554</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
@@ -617,7 +615,7 @@
       <c r="G4" s="1">
         <v>40962</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
@@ -646,7 +644,7 @@
       <c r="G5" s="1">
         <v>41336</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5">
         <f>_xlfn.DAYS(G5,F5)</f>
         <v>49</v>
       </c>
@@ -675,7 +673,7 @@
       <c r="G6" s="1">
         <v>41339</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
@@ -704,7 +702,7 @@
       <c r="G7" s="1">
         <v>41642</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
@@ -733,7 +731,7 @@
       <c r="G8" s="1">
         <v>41631</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
@@ -762,7 +760,7 @@
       <c r="G9" s="1">
         <v>41622</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
@@ -791,7 +789,7 @@
       <c r="G10" s="1">
         <v>41625</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
@@ -820,7 +818,7 @@
       <c r="G11" s="1">
         <v>42049</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
@@ -849,7 +847,7 @@
       <c r="G12" s="1">
         <v>42029</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
@@ -878,7 +876,7 @@
       <c r="G13" s="1">
         <v>42072</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13">
         <f t="shared" si="0"/>
         <v>99</v>
       </c>
@@ -907,7 +905,7 @@
       <c r="G14" s="1">
         <v>42064</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
@@ -936,7 +934,7 @@
       <c r="G15" s="1">
         <v>42070</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15">
         <f t="shared" si="0"/>
         <v>97</v>
       </c>
@@ -965,7 +963,7 @@
       <c r="G16" s="1">
         <v>42070</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16">
         <f t="shared" si="0"/>
         <v>97</v>
       </c>
@@ -994,7 +992,7 @@
       <c r="G17" s="1">
         <v>42064</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17">
         <f t="shared" si="0"/>
         <v>92</v>
       </c>
@@ -1023,7 +1021,7 @@
       <c r="G18" s="1">
         <v>42394</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -1052,7 +1050,7 @@
       <c r="G19" s="1">
         <v>42763</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
@@ -1081,7 +1079,7 @@
       <c r="G20" s="1">
         <v>43162</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
@@ -1108,7 +1106,7 @@
       <c r="G21" s="1">
         <v>43161</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>

--- a/data/Date_landmarks_20essais.xlsx
+++ b/data/Date_landmarks_20essais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN.RDS-PRET-0218\Desktop\Agrocampus Ouest\M2\Projet ingénieur\meteo_vs_rendement\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1DBEE1D-65E4-4CD6-896C-A32D99521B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4775EFB4-BE81-46C8-B646-FA8603E4ECF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>RAGT14</t>
   </si>
@@ -183,6 +183,9 @@
   </si>
   <si>
     <t>YEAR</t>
+  </si>
+  <si>
+    <t>FIN_P1000</t>
   </si>
 </sst>
 </file>
@@ -505,7 +508,8 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="8" width="17.81640625" customWidth="1"/>
-    <col min="9" max="10" width="28.1796875" customWidth="1"/>
+    <col min="9" max="9" width="12.54296875" customWidth="1"/>
+    <col min="10" max="10" width="28.1796875" customWidth="1"/>
     <col min="11" max="11" width="16.7265625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -534,6 +538,9 @@
       <c r="H1" t="s">
         <v>44</v>
       </c>
+      <c r="I1" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
@@ -561,7 +568,9 @@
         <f t="shared" ref="H2:H21" si="0">_xlfn.DAYS(G2,F2)</f>
         <v>43</v>
       </c>
-      <c r="I2" s="1"/>
+      <c r="I2" s="1">
+        <v>40703</v>
+      </c>
       <c r="J2" s="1"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -590,7 +599,9 @@
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="I3" s="1"/>
+      <c r="I3" s="1">
+        <v>40718</v>
+      </c>
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
@@ -619,7 +630,9 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="I4" s="1"/>
+      <c r="I4" s="1">
+        <v>41089</v>
+      </c>
       <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
@@ -648,7 +661,9 @@
         <f>_xlfn.DAYS(G5,F5)</f>
         <v>49</v>
       </c>
-      <c r="I5" s="1"/>
+      <c r="I5" s="1">
+        <v>41461</v>
+      </c>
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -677,7 +692,9 @@
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="I6" s="1"/>
+      <c r="I6" s="1">
+        <v>41472</v>
+      </c>
       <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
@@ -706,7 +723,9 @@
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="I7" s="1"/>
+      <c r="I7" s="1">
+        <v>41810</v>
+      </c>
       <c r="J7" s="1"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
@@ -735,7 +754,9 @@
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="I8" s="1"/>
+      <c r="I8" s="1">
+        <v>41818</v>
+      </c>
       <c r="J8" s="1"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
@@ -764,7 +785,9 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="I9" s="1"/>
+      <c r="I9" s="1">
+        <v>41819</v>
+      </c>
       <c r="J9" s="1"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
@@ -793,7 +816,9 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="I10" s="1"/>
+      <c r="I10" s="1">
+        <v>41826</v>
+      </c>
       <c r="J10" s="1"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
@@ -822,7 +847,9 @@
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="I11" s="1"/>
+      <c r="I11" s="1">
+        <v>42167</v>
+      </c>
       <c r="J11" s="1"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
@@ -851,7 +878,9 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="I12" s="1"/>
+      <c r="I12" s="1">
+        <v>42186</v>
+      </c>
       <c r="J12" s="1"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
@@ -880,7 +909,9 @@
         <f t="shared" si="0"/>
         <v>99</v>
       </c>
-      <c r="I13" s="1"/>
+      <c r="I13" s="1">
+        <v>42189</v>
+      </c>
       <c r="J13" s="1"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
@@ -909,7 +940,9 @@
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="I14" s="1"/>
+      <c r="I14" s="1">
+        <v>42187</v>
+      </c>
       <c r="J14" s="1"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
@@ -938,7 +971,9 @@
         <f t="shared" si="0"/>
         <v>97</v>
       </c>
-      <c r="I15" s="1"/>
+      <c r="I15" s="1">
+        <v>42193</v>
+      </c>
       <c r="J15" s="1"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
@@ -967,7 +1002,9 @@
         <f t="shared" si="0"/>
         <v>97</v>
       </c>
-      <c r="I16" s="1"/>
+      <c r="I16" s="1">
+        <v>42194</v>
+      </c>
       <c r="J16" s="1"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
@@ -996,7 +1033,9 @@
         <f t="shared" si="0"/>
         <v>92</v>
       </c>
-      <c r="I17" s="1"/>
+      <c r="I17" s="1">
+        <v>42184</v>
+      </c>
       <c r="J17" s="1"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
@@ -1025,7 +1064,9 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="I18" s="1"/>
+      <c r="I18" s="1">
+        <v>42547</v>
+      </c>
       <c r="J18" s="1"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
@@ -1054,7 +1095,9 @@
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="I19" s="1"/>
+      <c r="I19" s="1">
+        <v>42911</v>
+      </c>
       <c r="J19" s="1"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
@@ -1083,6 +1126,9 @@
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
+      <c r="I20" s="1">
+        <v>43276</v>
+      </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21">
@@ -1109,6 +1155,9 @@
       <c r="H21">
         <f t="shared" si="0"/>
         <v>93</v>
+      </c>
+      <c r="I21" s="1">
+        <v>43280</v>
       </c>
     </row>
   </sheetData>

--- a/data/Date_landmarks_20essais.xlsx
+++ b/data/Date_landmarks_20essais.xlsx
@@ -243,6 +243,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -302,16 +303,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -441,680 +446,680 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="26.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="20.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="26.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="18.87"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>2011</v>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="E2" s="2" t="n">
         <v>40429</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="3" t="n">
         <v>40506</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="3" t="n">
         <v>40549</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="3" t="n">
         <v>40623</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="3" t="n">
         <v>40644</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" s="3" t="n">
         <v>40703</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>2011</v>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="E3" s="2" t="n">
         <v>40435</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="3" t="n">
         <v>40505</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="3" t="n">
         <v>40554</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="3" t="n">
         <v>40628</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I3" s="3" t="n">
         <v>40649</v>
       </c>
-      <c r="J3" s="2" t="n">
-        <v>40718</v>
+      <c r="J3" s="3" t="n">
+        <v>40717</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>2012</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="E4" s="2" t="n">
         <v>40802</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="3" t="n">
         <v>40922</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="3" t="n">
         <v>40962</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="3" t="n">
         <v>40993</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" s="3" t="n">
         <v>41014</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J4" s="3" t="n">
         <v>41089</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>2013</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5" s="2" t="n">
         <v>41169</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="3" t="n">
         <v>41287</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="3" t="n">
         <v>41336</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="3" t="n">
         <v>41364</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="3" t="n">
         <v>41385</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="J5" s="3" t="n">
         <v>41461</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <v>2013</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6" s="2" t="n">
         <v>41170</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="3" t="n">
         <v>41281</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="3" t="n">
         <v>41339</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="3" t="n">
         <v>41388</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="3" t="n">
         <v>41409</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="J6" s="3" t="n">
         <v>41472</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>2014</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="E7" s="2" t="n">
         <v>41536</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="3" t="n">
         <v>41594</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="3" t="n">
         <v>41642</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="3" t="n">
         <v>41717</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="I7" s="3" t="n">
         <v>41738</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="J7" s="3" t="n">
         <v>41810</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>2014</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="2" t="n">
         <v>41537</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="3" t="n">
         <v>41594</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="3" t="n">
         <v>41631</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="3" t="n">
         <v>41729</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" s="3" t="n">
         <v>41750</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="J8" s="3" t="n">
         <v>41818</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>2014</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="E9" s="2" t="n">
         <v>41538</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="3" t="n">
         <v>41598</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="3" t="n">
         <v>41622</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="3" t="n">
         <v>41731</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="I9" s="3" t="n">
         <v>41752</v>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="J9" s="3" t="n">
         <v>41819</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <v>2014</v>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="E10" s="2" t="n">
         <v>41539</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="3" t="n">
         <v>41594</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G10" s="3" t="n">
         <v>41625</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="3" t="n">
         <v>41736</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="I10" s="3" t="n">
         <v>41757</v>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="J10" s="3" t="n">
         <v>41826</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="E11" s="2" t="n">
         <v>41905</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="3" t="n">
         <v>41995</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="G11" s="3" t="n">
         <v>42049</v>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="H11" s="3" t="n">
         <v>42089</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="I11" s="3" t="n">
         <v>42110</v>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="J11" s="3" t="n">
         <v>42167</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="E12" s="1" t="n">
+      <c r="E12" s="2" t="n">
         <v>41906</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F12" s="3" t="n">
         <v>42001</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="G12" s="3" t="n">
         <v>42029</v>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="H12" s="3" t="n">
         <v>42097</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="I12" s="3" t="n">
         <v>42118</v>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="J12" s="3" t="n">
         <v>42186</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="0" t="n">
+      <c r="D13" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="E13" s="1" t="n">
+      <c r="E13" s="2" t="n">
         <v>41907</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" s="3" t="n">
         <v>41973</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="G13" s="3" t="n">
         <v>42072</v>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="H13" s="3" t="n">
         <v>42108</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="I13" s="3" t="n">
         <v>42129</v>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="J13" s="3" t="n">
         <v>42189</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="0" t="n">
+      <c r="D14" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="E14" s="1" t="n">
+      <c r="E14" s="2" t="n">
         <v>41908</v>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="F14" s="3" t="n">
         <v>41973</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="G14" s="3" t="n">
         <v>42064</v>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="H14" s="3" t="n">
         <v>42104</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="I14" s="3" t="n">
         <v>42125</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="J14" s="3" t="n">
         <v>42187</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="0" t="n">
+      <c r="D15" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="E15" s="1" t="n">
+      <c r="E15" s="2" t="n">
         <v>41909</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="F15" s="3" t="n">
         <v>41973</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="G15" s="3" t="n">
         <v>42070</v>
       </c>
-      <c r="H15" s="2" t="n">
+      <c r="H15" s="3" t="n">
         <v>42109</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="I15" s="3" t="n">
         <v>42130</v>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="J15" s="3" t="n">
         <v>42193</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="0" t="n">
+      <c r="D16" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="E16" s="1" t="n">
+      <c r="E16" s="2" t="n">
         <v>41910</v>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="F16" s="3" t="n">
         <v>41973</v>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="G16" s="3" t="n">
         <v>42070</v>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="H16" s="3" t="n">
         <v>42107</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="I16" s="3" t="n">
         <v>42128</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="J16" s="3" t="n">
         <v>42194</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="0" t="n">
+      <c r="D17" s="1" t="n">
         <v>2015</v>
       </c>
-      <c r="E17" s="1" t="n">
+      <c r="E17" s="2" t="n">
         <v>41911</v>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="F17" s="3" t="n">
         <v>41972</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="G17" s="3" t="n">
         <v>42064</v>
       </c>
-      <c r="H17" s="2" t="n">
+      <c r="H17" s="3" t="n">
         <v>42105</v>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="I17" s="3" t="n">
         <v>42126</v>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="J17" s="3" t="n">
         <v>42184</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="0" t="n">
+      <c r="D18" s="1" t="n">
         <v>2016</v>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="E18" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="F18" s="3" t="n">
         <v>42382</v>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="G18" s="3" t="n">
         <v>42394</v>
       </c>
-      <c r="H18" s="2" t="n">
+      <c r="H18" s="3" t="n">
         <v>42451</v>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="I18" s="3" t="n">
         <v>42472</v>
       </c>
-      <c r="J18" s="2" t="n">
+      <c r="J18" s="3" t="n">
         <v>42547</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D19" s="0" t="n">
+      <c r="D19" s="1" t="n">
         <v>2017</v>
       </c>
-      <c r="E19" s="1" t="n">
+      <c r="E19" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="F19" s="3" t="n">
         <v>42702</v>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="G19" s="3" t="n">
         <v>42763</v>
       </c>
-      <c r="H19" s="2" t="n">
+      <c r="H19" s="3" t="n">
         <v>42824</v>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="I19" s="3" t="n">
         <v>42845</v>
       </c>
-      <c r="J19" s="2" t="n">
+      <c r="J19" s="3" t="n">
         <v>42911</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="0" t="n">
+      <c r="D20" s="1" t="n">
         <v>2018</v>
       </c>
-      <c r="E20" s="1" t="n">
+      <c r="E20" s="2" t="n">
         <v>43010</v>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="F20" s="3" t="n">
         <v>43068</v>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="G20" s="3" t="n">
         <v>43162</v>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="H20" s="3" t="n">
         <v>43192</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="I20" s="3" t="n">
         <v>43213</v>
       </c>
-      <c r="J20" s="2" t="n">
+      <c r="J20" s="3" t="n">
         <v>43276</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="0" t="n">
+      <c r="D21" s="1" t="n">
         <v>2018</v>
       </c>
-      <c r="E21" s="1" t="n">
+      <c r="E21" s="2" t="n">
         <v>43011</v>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="F21" s="3" t="n">
         <v>43068</v>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="G21" s="3" t="n">
         <v>43161</v>
       </c>
-      <c r="H21" s="2" t="n">
+      <c r="H21" s="3" t="n">
         <v>43196</v>
       </c>
-      <c r="I21" s="2" t="n">
+      <c r="I21" s="3" t="n">
         <v>43217</v>
       </c>
-      <c r="J21" s="2" t="n">
+      <c r="J21" s="3" t="n">
         <v>43280</v>
       </c>
     </row>
